--- a/data/nzd0024/nzd0024.xlsx
+++ b/data/nzd0024/nzd0024.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M498"/>
+  <dimension ref="A1:M499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22858,6 +22858,51 @@
         <v>399.82</v>
       </c>
       <c r="M498" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>371.63</v>
+      </c>
+      <c r="C499" t="n">
+        <v>377.71</v>
+      </c>
+      <c r="D499" t="n">
+        <v>384.34</v>
+      </c>
+      <c r="E499" t="n">
+        <v>387.86</v>
+      </c>
+      <c r="F499" t="n">
+        <v>388.32</v>
+      </c>
+      <c r="G499" t="n">
+        <v>381.13</v>
+      </c>
+      <c r="H499" t="n">
+        <v>379.72</v>
+      </c>
+      <c r="I499" t="n">
+        <v>381.31</v>
+      </c>
+      <c r="J499" t="n">
+        <v>388.18</v>
+      </c>
+      <c r="K499" t="n">
+        <v>393.29</v>
+      </c>
+      <c r="L499" t="n">
+        <v>398.66</v>
+      </c>
+      <c r="M499" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -22874,7 +22919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B577"/>
+  <dimension ref="A1:B578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28647,6 +28692,16 @@
       </c>
       <c r="B577" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -28815,28 +28870,28 @@
         <v>0.0737</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07418090323503242</v>
+        <v>0.07284248559361965</v>
       </c>
       <c r="J2" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K2" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008100388563007432</v>
+        <v>0.007845569035490052</v>
       </c>
       <c r="M2" t="n">
-        <v>4.981532438417521</v>
+        <v>4.977907380222073</v>
       </c>
       <c r="N2" t="n">
-        <v>38.1278255860573</v>
+        <v>38.07258851414097</v>
       </c>
       <c r="O2" t="n">
-        <v>6.174773322645723</v>
+        <v>6.170298899902741</v>
       </c>
       <c r="P2" t="n">
-        <v>372.9449263299858</v>
+        <v>372.9581133577586</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28893,28 +28948,28 @@
         <v>0.0822</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1105202617636995</v>
+        <v>0.1091745343863327</v>
       </c>
       <c r="J3" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K3" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02521115996391043</v>
+        <v>0.0247109078498492</v>
       </c>
       <c r="M3" t="n">
-        <v>4.048921488379454</v>
+        <v>4.048401125924121</v>
       </c>
       <c r="N3" t="n">
-        <v>26.72375405170938</v>
+        <v>26.69165028796506</v>
       </c>
       <c r="O3" t="n">
-        <v>5.16950230212826</v>
+        <v>5.166396257350482</v>
       </c>
       <c r="P3" t="n">
-        <v>378.0843142447139</v>
+        <v>378.0975732931237</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28971,28 +29026,28 @@
         <v>0.0805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1213967446909017</v>
+        <v>0.1197436548484955</v>
       </c>
       <c r="J4" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K4" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02441326464394455</v>
+        <v>0.02385640988691429</v>
       </c>
       <c r="M4" t="n">
-        <v>4.633571518060686</v>
+        <v>4.632843100611945</v>
       </c>
       <c r="N4" t="n">
-        <v>33.32345675445973</v>
+        <v>33.28907301112027</v>
       </c>
       <c r="O4" t="n">
-        <v>5.772647291707655</v>
+        <v>5.769668362316873</v>
       </c>
       <c r="P4" t="n">
-        <v>385.1847780593125</v>
+        <v>385.2010654579452</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29049,28 +29104,28 @@
         <v>0.0893</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1671720906763091</v>
+        <v>0.165037804792584</v>
       </c>
       <c r="J5" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K5" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04076102205024035</v>
+        <v>0.03989405454278794</v>
       </c>
       <c r="M5" t="n">
-        <v>4.862552023438639</v>
+        <v>4.864627710020482</v>
       </c>
       <c r="N5" t="n">
-        <v>37.21390428064614</v>
+        <v>37.19340354312674</v>
       </c>
       <c r="O5" t="n">
-        <v>6.100320014609573</v>
+        <v>6.098639482960666</v>
       </c>
       <c r="P5" t="n">
-        <v>388.6734855134336</v>
+        <v>388.6945139924024</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29127,28 +29182,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2963840969549736</v>
+        <v>0.2928906795105257</v>
       </c>
       <c r="J6" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K6" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1191256208829314</v>
+        <v>0.1167423248092682</v>
       </c>
       <c r="M6" t="n">
-        <v>5.019337589444026</v>
+        <v>5.026937126906837</v>
       </c>
       <c r="N6" t="n">
-        <v>36.75483955093571</v>
+        <v>36.82631376471051</v>
       </c>
       <c r="O6" t="n">
-        <v>6.062576972784404</v>
+        <v>6.068468815501197</v>
       </c>
       <c r="P6" t="n">
-        <v>389.0506224126734</v>
+        <v>389.0850420074522</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29205,28 +29260,28 @@
         <v>0.0825</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2084794437387463</v>
+        <v>0.2033842507295324</v>
       </c>
       <c r="J7" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K7" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05212985860388519</v>
+        <v>0.04963676888143254</v>
       </c>
       <c r="M7" t="n">
-        <v>5.553417493055426</v>
+        <v>5.563248434819706</v>
       </c>
       <c r="N7" t="n">
-        <v>44.71824088576496</v>
+        <v>44.93749147895816</v>
       </c>
       <c r="O7" t="n">
-        <v>6.687169871161115</v>
+        <v>6.703543203333455</v>
       </c>
       <c r="P7" t="n">
-        <v>388.0921304745929</v>
+        <v>388.1423318838105</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29283,28 +29338,28 @@
         <v>0.1961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3215394169393088</v>
+        <v>0.3173031816245967</v>
       </c>
       <c r="J8" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K8" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1355541972570738</v>
+        <v>0.1323649515095192</v>
       </c>
       <c r="M8" t="n">
-        <v>4.877238791178129</v>
+        <v>4.88362612278183</v>
       </c>
       <c r="N8" t="n">
-        <v>37.30690113225846</v>
+        <v>37.44561773570953</v>
       </c>
       <c r="O8" t="n">
-        <v>6.107937551437347</v>
+        <v>6.119282452682629</v>
       </c>
       <c r="P8" t="n">
-        <v>381.6003433226987</v>
+        <v>381.6420816792617</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29361,28 +29416,28 @@
         <v>0.1295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3601115486188394</v>
+        <v>0.3546101719305695</v>
       </c>
       <c r="J9" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K9" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1267831165773362</v>
+        <v>0.1231580477373159</v>
       </c>
       <c r="M9" t="n">
-        <v>5.588868332840333</v>
+        <v>5.599510363425639</v>
       </c>
       <c r="N9" t="n">
-        <v>50.53947603715956</v>
+        <v>50.79827514446549</v>
       </c>
       <c r="O9" t="n">
-        <v>7.109112183469857</v>
+        <v>7.127290869921437</v>
       </c>
       <c r="P9" t="n">
-        <v>385.2716570751263</v>
+        <v>385.3258604903627</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29439,28 +29494,28 @@
         <v>0.1507</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2718656057133235</v>
+        <v>0.2670562499484874</v>
       </c>
       <c r="J10" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K10" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07713023786521811</v>
+        <v>0.07457600835368527</v>
       </c>
       <c r="M10" t="n">
-        <v>5.510231474586222</v>
+        <v>5.520299104786401</v>
       </c>
       <c r="N10" t="n">
-        <v>50.04033597182595</v>
+        <v>50.21519762352726</v>
       </c>
       <c r="O10" t="n">
-        <v>7.073919420789719</v>
+        <v>7.08626824383097</v>
       </c>
       <c r="P10" t="n">
-        <v>392.7757951885778</v>
+        <v>392.8231803291186</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29517,28 +29572,28 @@
         <v>0.1119</v>
       </c>
       <c r="I11" t="n">
-        <v>0.276302009610081</v>
+        <v>0.2724550120366832</v>
       </c>
       <c r="J11" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K11" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09118339469716952</v>
+        <v>0.08893980302805415</v>
       </c>
       <c r="M11" t="n">
-        <v>5.218430002961134</v>
+        <v>5.226133208202981</v>
       </c>
       <c r="N11" t="n">
-        <v>43.05509186120323</v>
+        <v>43.14481156474509</v>
       </c>
       <c r="O11" t="n">
-        <v>6.561637894703062</v>
+        <v>6.568471021839488</v>
       </c>
       <c r="P11" t="n">
-        <v>395.4108481586118</v>
+        <v>395.4487514724003</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29595,28 +29650,28 @@
         <v>0.1089</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2639845943786706</v>
+        <v>0.2601956044076301</v>
       </c>
       <c r="J12" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K12" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07535773955805436</v>
+        <v>0.07345072177674461</v>
       </c>
       <c r="M12" t="n">
-        <v>5.474972976115658</v>
+        <v>5.48115472997511</v>
       </c>
       <c r="N12" t="n">
-        <v>48.38368900888899</v>
+        <v>48.45743578416059</v>
       </c>
       <c r="O12" t="n">
-        <v>6.955838483525117</v>
+        <v>6.961137535213665</v>
       </c>
       <c r="P12" t="n">
-        <v>400.9651455964878</v>
+        <v>401.0024773787605</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29654,7 +29709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M498"/>
+  <dimension ref="A1:M499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63023,6 +63078,73 @@
         </is>
       </c>
     </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-34.82206255074712,173.40823212946108</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-34.82265147923821,173.40772181242815</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-34.82330132122317,173.4073914878874</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-34.82398802598121,173.4071871405302</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-34.8246897349533,173.4070554750838</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-34.825402210988265,173.40695191370511</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-34.826129417063754,173.40697971435947</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>-34.82683809841861,173.40708610954073</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>-34.827464191905314,173.40742994060778</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>-34.827955185672245,173.40796863322552</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>-34.82830736662179,173.40869788066632</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0024/nzd0024.xlsx
+++ b/data/nzd0024/nzd0024.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M499"/>
+  <dimension ref="A1:M503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22903,6 +22903,186 @@
         <v>398.66</v>
       </c>
       <c r="M499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="C500" t="n">
+        <v>375.99</v>
+      </c>
+      <c r="D500" t="n">
+        <v>383.52</v>
+      </c>
+      <c r="E500" t="n">
+        <v>386.87</v>
+      </c>
+      <c r="F500" t="n">
+        <v>388.25</v>
+      </c>
+      <c r="G500" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="H500" t="n">
+        <v>379.18</v>
+      </c>
+      <c r="I500" t="n">
+        <v>381.09</v>
+      </c>
+      <c r="J500" t="n">
+        <v>388.04</v>
+      </c>
+      <c r="K500" t="n">
+        <v>393.19</v>
+      </c>
+      <c r="L500" t="n">
+        <v>397.88</v>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="C501" t="n">
+        <v>375.99</v>
+      </c>
+      <c r="D501" t="n">
+        <v>383.52</v>
+      </c>
+      <c r="E501" t="n">
+        <v>386.87</v>
+      </c>
+      <c r="F501" t="n">
+        <v>388.25</v>
+      </c>
+      <c r="G501" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="H501" t="n">
+        <v>379.18</v>
+      </c>
+      <c r="I501" t="n">
+        <v>381.09</v>
+      </c>
+      <c r="J501" t="n">
+        <v>388.61</v>
+      </c>
+      <c r="K501" t="n">
+        <v>393.7</v>
+      </c>
+      <c r="L501" t="n">
+        <v>398.27</v>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>371.39</v>
+      </c>
+      <c r="C502" t="n">
+        <v>376.23</v>
+      </c>
+      <c r="D502" t="n">
+        <v>383.78</v>
+      </c>
+      <c r="E502" t="n">
+        <v>386.96</v>
+      </c>
+      <c r="F502" t="n">
+        <v>388.18</v>
+      </c>
+      <c r="G502" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="H502" t="n">
+        <v>380.9</v>
+      </c>
+      <c r="I502" t="n">
+        <v>381.89</v>
+      </c>
+      <c r="J502" t="n">
+        <v>389.38</v>
+      </c>
+      <c r="K502" t="n">
+        <v>393.11</v>
+      </c>
+      <c r="L502" t="n">
+        <v>397.62</v>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>371.39</v>
+      </c>
+      <c r="C503" t="n">
+        <v>376.23</v>
+      </c>
+      <c r="D503" t="n">
+        <v>381.87</v>
+      </c>
+      <c r="E503" t="n">
+        <v>386.96</v>
+      </c>
+      <c r="F503" t="n">
+        <v>388.18</v>
+      </c>
+      <c r="G503" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="H503" t="n">
+        <v>380.9</v>
+      </c>
+      <c r="I503" t="n">
+        <v>381.89</v>
+      </c>
+      <c r="J503" t="n">
+        <v>389.38</v>
+      </c>
+      <c r="K503" t="n">
+        <v>393.11</v>
+      </c>
+      <c r="L503" t="n">
+        <v>397.62</v>
+      </c>
+      <c r="M503" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -22919,7 +23099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B578"/>
+  <dimension ref="A1:B582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28702,6 +28882,46 @@
       </c>
       <c r="B578" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -28870,28 +29090,28 @@
         <v>0.0737</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07284248559361965</v>
+        <v>0.06713966713996104</v>
       </c>
       <c r="J2" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K2" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007845569035490052</v>
+        <v>0.006781254436227901</v>
       </c>
       <c r="M2" t="n">
-        <v>4.977907380222073</v>
+        <v>4.965550466688104</v>
       </c>
       <c r="N2" t="n">
-        <v>38.07258851414097</v>
+        <v>37.86760061853079</v>
       </c>
       <c r="O2" t="n">
-        <v>6.170298899902741</v>
+        <v>6.153665624530698</v>
       </c>
       <c r="P2" t="n">
-        <v>372.9581133577586</v>
+        <v>373.0144360944493</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28948,28 +29168,28 @@
         <v>0.0822</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1091745343863327</v>
+        <v>0.1013846929651798</v>
       </c>
       <c r="J3" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K3" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0247109078498492</v>
+        <v>0.02163311439876114</v>
       </c>
       <c r="M3" t="n">
-        <v>4.048401125924121</v>
+        <v>4.060088571434252</v>
       </c>
       <c r="N3" t="n">
-        <v>26.69165028796506</v>
+        <v>26.66257137143021</v>
       </c>
       <c r="O3" t="n">
-        <v>5.166396257350482</v>
+        <v>5.163581254461889</v>
       </c>
       <c r="P3" t="n">
-        <v>378.0975732931237</v>
+        <v>378.1745079136182</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29026,28 +29246,28 @@
         <v>0.0805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1197436548484955</v>
+        <v>0.1114371515682152</v>
       </c>
       <c r="J4" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K4" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02385640988691429</v>
+        <v>0.02097994391187008</v>
       </c>
       <c r="M4" t="n">
-        <v>4.632843100611945</v>
+        <v>4.638595141188627</v>
       </c>
       <c r="N4" t="n">
-        <v>33.28907301112027</v>
+        <v>33.23700050258535</v>
       </c>
       <c r="O4" t="n">
-        <v>5.769668362316873</v>
+        <v>5.765153987760028</v>
       </c>
       <c r="P4" t="n">
-        <v>385.2010654579452</v>
+        <v>385.2831068326718</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29104,28 +29324,28 @@
         <v>0.0893</v>
       </c>
       <c r="I5" t="n">
-        <v>0.165037804792584</v>
+        <v>0.1552123760466047</v>
       </c>
       <c r="J5" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K5" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03989405454278794</v>
+        <v>0.03582363349271045</v>
       </c>
       <c r="M5" t="n">
-        <v>4.864627710020482</v>
+        <v>4.880335267537586</v>
       </c>
       <c r="N5" t="n">
-        <v>37.19340354312674</v>
+        <v>37.18896536714607</v>
       </c>
       <c r="O5" t="n">
-        <v>6.098639482960666</v>
+        <v>6.098275606033732</v>
       </c>
       <c r="P5" t="n">
-        <v>388.6945139924024</v>
+        <v>388.7915534316384</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29182,28 +29402,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2928906795105257</v>
+        <v>0.2791189067530396</v>
       </c>
       <c r="J6" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K6" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1167423248092682</v>
+        <v>0.1074788991913871</v>
       </c>
       <c r="M6" t="n">
-        <v>5.026937126906837</v>
+        <v>5.05622312496596</v>
       </c>
       <c r="N6" t="n">
-        <v>36.82631376471051</v>
+        <v>37.10635933869018</v>
       </c>
       <c r="O6" t="n">
-        <v>6.068468815501197</v>
+        <v>6.09149894021908</v>
       </c>
       <c r="P6" t="n">
-        <v>389.0850420074522</v>
+        <v>389.2210576885033</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29260,28 +29480,28 @@
         <v>0.0825</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2033842507295324</v>
+        <v>0.1855140739559883</v>
       </c>
       <c r="J7" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K7" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04963676888143254</v>
+        <v>0.04153553903006335</v>
       </c>
       <c r="M7" t="n">
-        <v>5.563248434819706</v>
+        <v>5.592234255114924</v>
       </c>
       <c r="N7" t="n">
-        <v>44.93749147895816</v>
+        <v>45.5495867690615</v>
       </c>
       <c r="O7" t="n">
-        <v>6.703543203333455</v>
+        <v>6.749043396590475</v>
       </c>
       <c r="P7" t="n">
-        <v>388.1423318838105</v>
+        <v>388.3188190870875</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29338,28 +29558,28 @@
         <v>0.1961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3173031816245967</v>
+        <v>0.3013284192984057</v>
       </c>
       <c r="J8" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K8" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1323649515095192</v>
+        <v>0.120739208988663</v>
       </c>
       <c r="M8" t="n">
-        <v>4.88362612278183</v>
+        <v>4.906508141809136</v>
       </c>
       <c r="N8" t="n">
-        <v>37.44561773570953</v>
+        <v>37.92487167586446</v>
       </c>
       <c r="O8" t="n">
-        <v>6.119282452682629</v>
+        <v>6.158317276323498</v>
       </c>
       <c r="P8" t="n">
-        <v>381.6420816792617</v>
+        <v>381.7998481828287</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29416,28 +29636,28 @@
         <v>0.1295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3546101719305695</v>
+        <v>0.3334836629914034</v>
       </c>
       <c r="J9" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K9" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1231580477373159</v>
+        <v>0.109742795263445</v>
       </c>
       <c r="M9" t="n">
-        <v>5.599510363425639</v>
+        <v>5.638285839168102</v>
       </c>
       <c r="N9" t="n">
-        <v>50.79827514446549</v>
+        <v>51.74437645671514</v>
       </c>
       <c r="O9" t="n">
-        <v>7.127290869921437</v>
+        <v>7.193356411072313</v>
       </c>
       <c r="P9" t="n">
-        <v>385.3258604903627</v>
+        <v>385.5345111811784</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29494,28 +29714,28 @@
         <v>0.1507</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2670562499484874</v>
+        <v>0.2494129781233854</v>
       </c>
       <c r="J10" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K10" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07457600835368527</v>
+        <v>0.06567478850194253</v>
       </c>
       <c r="M10" t="n">
-        <v>5.520299104786401</v>
+        <v>5.554460691451647</v>
       </c>
       <c r="N10" t="n">
-        <v>50.21519762352726</v>
+        <v>50.7588803353638</v>
       </c>
       <c r="O10" t="n">
-        <v>7.08626824383097</v>
+        <v>7.12452667447907</v>
       </c>
       <c r="P10" t="n">
-        <v>392.8231803291186</v>
+        <v>392.9974281015362</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29572,28 +29792,28 @@
         <v>0.1119</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2724550120366832</v>
+        <v>0.2574614820739082</v>
       </c>
       <c r="J11" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K11" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08893980302805415</v>
+        <v>0.08040681683220408</v>
       </c>
       <c r="M11" t="n">
-        <v>5.226133208202981</v>
+        <v>5.255849197759805</v>
       </c>
       <c r="N11" t="n">
-        <v>43.14481156474509</v>
+        <v>43.48124352943744</v>
       </c>
       <c r="O11" t="n">
-        <v>6.568471021839488</v>
+        <v>6.594030901462127</v>
       </c>
       <c r="P11" t="n">
-        <v>395.4487514724003</v>
+        <v>395.5968346110594</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29650,28 +29870,28 @@
         <v>0.1089</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2601956044076301</v>
+        <v>0.2441501105169762</v>
       </c>
       <c r="J12" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K12" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07345072177674461</v>
+        <v>0.06540970144395353</v>
       </c>
       <c r="M12" t="n">
-        <v>5.48115472997511</v>
+        <v>5.509270595237002</v>
       </c>
       <c r="N12" t="n">
-        <v>48.45743578416059</v>
+        <v>48.85033030462834</v>
       </c>
       <c r="O12" t="n">
-        <v>6.961137535213665</v>
+        <v>6.989301131345561</v>
       </c>
       <c r="P12" t="n">
-        <v>401.0024773787605</v>
+        <v>401.1609505866774</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29709,7 +29929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M499"/>
+  <dimension ref="A1:M503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63145,6 +63365,274 @@
         </is>
       </c>
     </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-34.82206037346752,173.4082289208121</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-34.822642958560934,173.4077060965986</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-34.8232985971285,173.40738315179152</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-34.823986096412604,173.40717657062575</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-34.82468967774722,173.4070547127665</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>-34.825402157440564,173.40695705290517</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>-34.826129800504916,173.40697382755957</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>-34.82683853521734,173.40708376276243</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>-34.827464797178116,173.40742859705395</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>-34.827955841533694,173.40796788270845</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>-34.82831315196352,173.40869302941877</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-34.82206037346752,173.4082289208121</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-34.822642958560934,173.4077060965986</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-34.8232985971285,173.40738315179152</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-34.823986096412604,173.40717657062575</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-34.82468967774722,173.4070547127665</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-34.825402157440564,173.40695705290517</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>-34.826129800504916,173.40697382755957</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>-34.82683853521734,173.40708376276243</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>-34.827462332853045,173.40743406723732</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>-34.82795249664027,173.40797171034544</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>-34.82831025929268,173.40869545504262</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-34.82206117562317,173.40823010294594</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-34.822644147492774,173.40770828950482</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-34.823299460865904,173.40738579494382</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-34.82398627182799,173.40717753152614</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-34.824689620541136,173.40705395044915</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>-34.82540198654219,173.4069734546074</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>-34.826128579172796,173.40699257810726</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>-34.8268369468581,173.4070922965016</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>-34.82745900385211,173.4074414567827</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>-34.82795636622283,173.40796728229478</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>-34.82831508041074,173.4086914123361</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-34.82206117562317,173.40823010294594</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-34.822644147492774,173.40770828950482</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-34.82329311571675,173.4073663779417</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-34.82398627182799,173.40717753152614</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-34.824689620541136,173.40705395044915</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>-34.82540198654219,173.4069734546074</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>-34.826128579172796,173.40699257810726</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>-34.8268369468581,173.4070922965016</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>-34.82745900385211,173.4074414567827</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>-34.82795636622283,173.40796728229478</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>-34.82831508041074,173.4086914123361</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0024/nzd0024.xlsx
+++ b/data/nzd0024/nzd0024.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M503"/>
+  <dimension ref="A1:M506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23085,6 +23085,141 @@
       <c r="M503" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>371.36</v>
+      </c>
+      <c r="C504" t="n">
+        <v>376.22</v>
+      </c>
+      <c r="D504" t="n">
+        <v>381.12</v>
+      </c>
+      <c r="E504" t="n">
+        <v>387</v>
+      </c>
+      <c r="F504" t="n">
+        <v>387.62</v>
+      </c>
+      <c r="G504" t="n">
+        <v>381.81</v>
+      </c>
+      <c r="H504" t="n">
+        <v>380.06</v>
+      </c>
+      <c r="I504" t="n">
+        <v>380.53</v>
+      </c>
+      <c r="J504" t="n">
+        <v>388.05</v>
+      </c>
+      <c r="K504" t="n">
+        <v>392.03</v>
+      </c>
+      <c r="L504" t="n">
+        <v>396.81</v>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>372.35</v>
+      </c>
+      <c r="C505" t="n">
+        <v>377.84</v>
+      </c>
+      <c r="D505" t="n">
+        <v>382.32</v>
+      </c>
+      <c r="E505" t="n">
+        <v>387.5</v>
+      </c>
+      <c r="F505" t="n">
+        <v>387.75</v>
+      </c>
+      <c r="G505" t="n">
+        <v>382.01</v>
+      </c>
+      <c r="H505" t="n">
+        <v>380.51</v>
+      </c>
+      <c r="I505" t="n">
+        <v>381.35</v>
+      </c>
+      <c r="J505" t="n">
+        <v>388.31</v>
+      </c>
+      <c r="K505" t="n">
+        <v>392.52</v>
+      </c>
+      <c r="L505" t="n">
+        <v>396.88</v>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>373.51</v>
+      </c>
+      <c r="C506" t="n">
+        <v>378.78</v>
+      </c>
+      <c r="D506" t="n">
+        <v>382.68</v>
+      </c>
+      <c r="E506" t="n">
+        <v>387.69</v>
+      </c>
+      <c r="F506" t="n">
+        <v>388.69</v>
+      </c>
+      <c r="G506" t="n">
+        <v>383.07</v>
+      </c>
+      <c r="H506" t="n">
+        <v>380.89</v>
+      </c>
+      <c r="I506" t="n">
+        <v>381.9</v>
+      </c>
+      <c r="J506" t="n">
+        <v>388.71</v>
+      </c>
+      <c r="K506" t="n">
+        <v>393.17</v>
+      </c>
+      <c r="L506" t="n">
+        <v>397.18</v>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23099,7 +23234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B582"/>
+  <dimension ref="A1:B586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28922,6 +29057,46 @@
       </c>
       <c r="B582" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -29090,28 +29265,28 @@
         <v>0.0737</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06713966713996104</v>
+        <v>0.06431456753250679</v>
       </c>
       <c r="J2" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K2" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006781254436227901</v>
+        <v>0.006306321496406309</v>
       </c>
       <c r="M2" t="n">
-        <v>4.965550466688104</v>
+        <v>4.949610734474249</v>
       </c>
       <c r="N2" t="n">
-        <v>37.86760061853079</v>
+        <v>37.68026724726895</v>
       </c>
       <c r="O2" t="n">
-        <v>6.153665624530698</v>
+        <v>6.138425469716884</v>
       </c>
       <c r="P2" t="n">
-        <v>373.0144360944493</v>
+        <v>373.042435201131</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29168,28 +29343,28 @@
         <v>0.0822</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1013846929651798</v>
+        <v>0.09753317370516885</v>
       </c>
       <c r="J3" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K3" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02163311439876114</v>
+        <v>0.02027678505311503</v>
       </c>
       <c r="M3" t="n">
-        <v>4.060088571434252</v>
+        <v>4.057570709327822</v>
       </c>
       <c r="N3" t="n">
-        <v>26.66257137143021</v>
+        <v>26.57222134575297</v>
       </c>
       <c r="O3" t="n">
-        <v>5.163581254461889</v>
+        <v>5.154825054815437</v>
       </c>
       <c r="P3" t="n">
-        <v>378.1745079136182</v>
+        <v>378.2126813754251</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29246,28 +29421,28 @@
         <v>0.0805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1114371515682152</v>
+        <v>0.1040883647321733</v>
       </c>
       <c r="J4" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K4" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02097994391187008</v>
+        <v>0.01848109161118361</v>
       </c>
       <c r="M4" t="n">
-        <v>4.638595141188627</v>
+        <v>4.648936758868138</v>
       </c>
       <c r="N4" t="n">
-        <v>33.23700050258535</v>
+        <v>33.2655163686885</v>
       </c>
       <c r="O4" t="n">
-        <v>5.765153987760028</v>
+        <v>5.767626580205111</v>
       </c>
       <c r="P4" t="n">
-        <v>385.2831068326718</v>
+        <v>385.355962446338</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29324,28 +29499,28 @@
         <v>0.0893</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1552123760466047</v>
+        <v>0.1486838275144836</v>
       </c>
       <c r="J5" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K5" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03582363349271045</v>
+        <v>0.03326268382479425</v>
       </c>
       <c r="M5" t="n">
-        <v>4.880335267537586</v>
+        <v>4.8876686464793</v>
       </c>
       <c r="N5" t="n">
-        <v>37.18896536714607</v>
+        <v>37.14475577962904</v>
       </c>
       <c r="O5" t="n">
-        <v>6.098275606033732</v>
+        <v>6.094649766773235</v>
       </c>
       <c r="P5" t="n">
-        <v>388.7915534316384</v>
+        <v>388.8562815654527</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29402,28 +29577,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2791189067530396</v>
+        <v>0.2689242916562214</v>
       </c>
       <c r="J6" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K6" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1074788991913871</v>
+        <v>0.1007516888745358</v>
       </c>
       <c r="M6" t="n">
-        <v>5.05622312496596</v>
+        <v>5.077743989010271</v>
       </c>
       <c r="N6" t="n">
-        <v>37.10635933869018</v>
+        <v>37.31695596507517</v>
       </c>
       <c r="O6" t="n">
-        <v>6.09149894021908</v>
+        <v>6.108760591566441</v>
       </c>
       <c r="P6" t="n">
-        <v>389.2210576885033</v>
+        <v>389.322134229968</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29480,28 +29655,28 @@
         <v>0.0825</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1855140739559883</v>
+        <v>0.1725405231600822</v>
       </c>
       <c r="J7" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K7" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04153553903006335</v>
+        <v>0.03608305139809997</v>
       </c>
       <c r="M7" t="n">
-        <v>5.592234255114924</v>
+        <v>5.612710622387909</v>
       </c>
       <c r="N7" t="n">
-        <v>45.5495867690615</v>
+        <v>45.97666100151258</v>
       </c>
       <c r="O7" t="n">
-        <v>6.749043396590475</v>
+        <v>6.780609191032365</v>
       </c>
       <c r="P7" t="n">
-        <v>388.3188190870875</v>
+        <v>388.4474484556101</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29558,28 +29733,28 @@
         <v>0.1961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3013284192984057</v>
+        <v>0.2902979814975813</v>
       </c>
       <c r="J8" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K8" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L8" t="n">
-        <v>0.120739208988663</v>
+        <v>0.1131042953634964</v>
       </c>
       <c r="M8" t="n">
-        <v>4.906508141809136</v>
+        <v>4.92100970192366</v>
       </c>
       <c r="N8" t="n">
-        <v>37.92487167586446</v>
+        <v>38.20325194807883</v>
       </c>
       <c r="O8" t="n">
-        <v>6.158317276323498</v>
+        <v>6.180877926967886</v>
       </c>
       <c r="P8" t="n">
-        <v>381.7998481828287</v>
+        <v>381.9092131049439</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29636,28 +29811,28 @@
         <v>0.1295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3334836629914034</v>
+        <v>0.3179314811658259</v>
       </c>
       <c r="J9" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K9" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L9" t="n">
-        <v>0.109742795263445</v>
+        <v>0.1002646543414303</v>
       </c>
       <c r="M9" t="n">
-        <v>5.638285839168102</v>
+        <v>5.665777988282497</v>
       </c>
       <c r="N9" t="n">
-        <v>51.74437645671514</v>
+        <v>52.43881087517025</v>
       </c>
       <c r="O9" t="n">
-        <v>7.193356411072313</v>
+        <v>7.241464691287962</v>
       </c>
       <c r="P9" t="n">
-        <v>385.5345111811784</v>
+        <v>385.688707125489</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29714,28 +29889,28 @@
         <v>0.1507</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2494129781233854</v>
+        <v>0.2360689589116613</v>
       </c>
       <c r="J10" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K10" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06567478850194253</v>
+        <v>0.05920694872111121</v>
       </c>
       <c r="M10" t="n">
-        <v>5.554460691451647</v>
+        <v>5.580754473101058</v>
       </c>
       <c r="N10" t="n">
-        <v>50.7588803353638</v>
+        <v>51.19387903384432</v>
       </c>
       <c r="O10" t="n">
-        <v>7.12452667447907</v>
+        <v>7.154989799702325</v>
       </c>
       <c r="P10" t="n">
-        <v>392.9974281015362</v>
+        <v>393.1297339024857</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29792,28 +29967,28 @@
         <v>0.1119</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2574614820739082</v>
+        <v>0.2457826757148033</v>
       </c>
       <c r="J11" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K11" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08040681683220408</v>
+        <v>0.07386513048024312</v>
       </c>
       <c r="M11" t="n">
-        <v>5.255849197759805</v>
+        <v>5.279866914775174</v>
       </c>
       <c r="N11" t="n">
-        <v>43.48124352943744</v>
+        <v>43.78810488409722</v>
       </c>
       <c r="O11" t="n">
-        <v>6.594030901462127</v>
+        <v>6.617258109224486</v>
       </c>
       <c r="P11" t="n">
-        <v>395.5968346110594</v>
+        <v>395.7126266186547</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29870,28 +30045,28 @@
         <v>0.1089</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2441501105169762</v>
+        <v>0.2314882669214886</v>
       </c>
       <c r="J12" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K12" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06540970144395353</v>
+        <v>0.05921079352244507</v>
       </c>
       <c r="M12" t="n">
-        <v>5.509270595237002</v>
+        <v>5.533102262168499</v>
       </c>
       <c r="N12" t="n">
-        <v>48.85033030462834</v>
+        <v>49.22302039693786</v>
       </c>
       <c r="O12" t="n">
-        <v>6.989301131345561</v>
+        <v>7.01591194335689</v>
       </c>
       <c r="P12" t="n">
-        <v>401.1609505866774</v>
+        <v>401.2864941590378</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29929,7 +30104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M503"/>
+  <dimension ref="A1:M506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63633,6 +63808,207 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-34.822061003732685,173.4082298496315</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-34.82264409795395,173.40770819813375</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-34.82329062416518,173.40735875346527</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-34.82398634979036,173.407177958593</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-34.824689162892255,173.40704785191056</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-34.82540213351492,173.4069593491435</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>-34.82612917563769,173.4069834208631</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>-34.82683964706847,173.40707778914484</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>-34.827464753944355,173.4074286930221</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>-34.82796344952613,173.40795917670945</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>-34.82832108826535,173.4086863745012</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-34.82206667611877,173.408238209007</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-34.82265212324282,173.40772300025262</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-34.82329461064746,173.40737095262782</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-34.82398732432,173.40718329692854</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-34.82468926913219,173.40704926764272</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>-34.825402110728554,173.40696153603713</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>-34.82612885610301,173.4069883265296</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>-34.826838019000654,173.4070865362277</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>-34.82746362986627,173.40743118819347</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>-34.82796023580526,173.40796285424372</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>-34.82832056906804,173.40868680986966</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-34.822073322550224,173.40824800383223</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-34.82265677989107,173.4077315891377</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-34.8232958065919,173.4073746123768</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-34.82398769464122,173.40718532549604</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-34.824690037328224,173.40705950447543</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>-34.82540198996018,173.40697312657335</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>-34.826128586273576,173.40699246909244</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>-34.8268369270036,173.40709240317332</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>-34.82746190051529,173.40743502691856</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>-34.82795597270598,173.40796773260502</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>-34.82831834393672,173.4086886757345</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0024/nzd0024.xlsx
+++ b/data/nzd0024/nzd0024.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M506"/>
+  <dimension ref="A1:M508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23218,6 +23218,96 @@
         <v>397.18</v>
       </c>
       <c r="M506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-09 22:11:38+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>375.95</v>
+      </c>
+      <c r="C507" t="n">
+        <v>379.69</v>
+      </c>
+      <c r="D507" t="n">
+        <v>384.66</v>
+      </c>
+      <c r="E507" t="n">
+        <v>389.58</v>
+      </c>
+      <c r="F507" t="n">
+        <v>387.5</v>
+      </c>
+      <c r="G507" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="H507" t="n">
+        <v>380.46</v>
+      </c>
+      <c r="I507" t="n">
+        <v>382.94</v>
+      </c>
+      <c r="J507" t="n">
+        <v>387.48</v>
+      </c>
+      <c r="K507" t="n">
+        <v>393.24</v>
+      </c>
+      <c r="L507" t="n">
+        <v>397.21</v>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>377.04</v>
+      </c>
+      <c r="C508" t="n">
+        <v>380.71</v>
+      </c>
+      <c r="D508" t="n">
+        <v>385.74</v>
+      </c>
+      <c r="E508" t="n">
+        <v>390.52</v>
+      </c>
+      <c r="F508" t="n">
+        <v>388.54</v>
+      </c>
+      <c r="G508" t="n">
+        <v>382.76</v>
+      </c>
+      <c r="H508" t="n">
+        <v>381.09</v>
+      </c>
+      <c r="I508" t="n">
+        <v>383.57</v>
+      </c>
+      <c r="J508" t="n">
+        <v>388.33</v>
+      </c>
+      <c r="K508" t="n">
+        <v>393.74</v>
+      </c>
+      <c r="L508" t="n">
+        <v>397.82</v>
+      </c>
+      <c r="M508" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23234,7 +23324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B586"/>
+  <dimension ref="A1:B588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29097,6 +29187,26 @@
       </c>
       <c r="B586" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-02-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
@@ -29265,28 +29375,28 @@
         <v>0.0737</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06431456753250679</v>
+        <v>0.06568745699729708</v>
       </c>
       <c r="J2" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K2" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006306321496406309</v>
+        <v>0.006634709091948299</v>
       </c>
       <c r="M2" t="n">
-        <v>4.949610734474249</v>
+        <v>4.937156159854426</v>
       </c>
       <c r="N2" t="n">
-        <v>37.68026724726895</v>
+        <v>37.54464028199069</v>
       </c>
       <c r="O2" t="n">
-        <v>6.138425469716884</v>
+        <v>6.127368136646491</v>
       </c>
       <c r="P2" t="n">
-        <v>373.042435201131</v>
+        <v>373.0287710188523</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29343,28 +29453,28 @@
         <v>0.0822</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09753317370516885</v>
+        <v>0.09706138126948115</v>
       </c>
       <c r="J3" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K3" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02027678505311503</v>
+        <v>0.02026499417581307</v>
       </c>
       <c r="M3" t="n">
-        <v>4.057570709327822</v>
+        <v>4.044248346965619</v>
       </c>
       <c r="N3" t="n">
-        <v>26.57222134575297</v>
+        <v>26.46982261019803</v>
       </c>
       <c r="O3" t="n">
-        <v>5.154825054815437</v>
+        <v>5.14488314835216</v>
       </c>
       <c r="P3" t="n">
-        <v>378.2126813754251</v>
+        <v>378.2173747942406</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29421,28 +29531,28 @@
         <v>0.0805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1040883647321733</v>
+        <v>0.1017922680989252</v>
       </c>
       <c r="J4" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K4" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01848109161118361</v>
+        <v>0.01783135739484321</v>
       </c>
       <c r="M4" t="n">
-        <v>4.648936758868138</v>
+        <v>4.642392198112853</v>
       </c>
       <c r="N4" t="n">
-        <v>33.2655163686885</v>
+        <v>33.16860419976206</v>
       </c>
       <c r="O4" t="n">
-        <v>5.767626580205111</v>
+        <v>5.759219061623031</v>
       </c>
       <c r="P4" t="n">
-        <v>385.355962446338</v>
+        <v>385.3788104723772</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29499,28 +29609,28 @@
         <v>0.0893</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1486838275144836</v>
+        <v>0.1465190967622057</v>
       </c>
       <c r="J5" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K5" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03326268382479425</v>
+        <v>0.03259534224317762</v>
       </c>
       <c r="M5" t="n">
-        <v>4.8876686464793</v>
+        <v>4.880304916549104</v>
       </c>
       <c r="N5" t="n">
-        <v>37.14475577962904</v>
+        <v>37.02857915284205</v>
       </c>
       <c r="O5" t="n">
-        <v>6.094649766773235</v>
+        <v>6.085111268731414</v>
       </c>
       <c r="P5" t="n">
-        <v>388.8562815654527</v>
+        <v>388.877822519189</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29577,28 +29687,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2689242916562214</v>
+        <v>0.2622846450919479</v>
       </c>
       <c r="J6" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K6" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1007516888745358</v>
+        <v>0.09646225213936055</v>
       </c>
       <c r="M6" t="n">
-        <v>5.077743989010271</v>
+        <v>5.091957388906228</v>
       </c>
       <c r="N6" t="n">
-        <v>37.31695596507517</v>
+        <v>37.44816920395539</v>
       </c>
       <c r="O6" t="n">
-        <v>6.108760591566441</v>
+        <v>6.119490926862739</v>
       </c>
       <c r="P6" t="n">
-        <v>389.322134229968</v>
+        <v>389.3882074768092</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29655,28 +29765,28 @@
         <v>0.0825</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1725405231600822</v>
+        <v>0.1641554631614079</v>
       </c>
       <c r="J7" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K7" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03608305139809997</v>
+        <v>0.03275970389434568</v>
       </c>
       <c r="M7" t="n">
-        <v>5.612710622387909</v>
+        <v>5.624933982740917</v>
       </c>
       <c r="N7" t="n">
-        <v>45.97666100151258</v>
+        <v>46.23821381894994</v>
       </c>
       <c r="O7" t="n">
-        <v>6.780609191032365</v>
+        <v>6.799868661889723</v>
       </c>
       <c r="P7" t="n">
-        <v>388.4474484556101</v>
+        <v>388.5308917446702</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29733,28 +29843,28 @@
         <v>0.1961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2902979814975813</v>
+        <v>0.2833426054283761</v>
       </c>
       <c r="J8" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K8" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1131042953634964</v>
+        <v>0.1084473254310864</v>
       </c>
       <c r="M8" t="n">
-        <v>4.92100970192366</v>
+        <v>4.92897662822191</v>
       </c>
       <c r="N8" t="n">
-        <v>38.20325194807883</v>
+        <v>38.35728692614185</v>
       </c>
       <c r="O8" t="n">
-        <v>6.180877926967886</v>
+        <v>6.193325998697457</v>
       </c>
       <c r="P8" t="n">
-        <v>381.9092131049439</v>
+        <v>381.9784290274922</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29811,28 +29921,28 @@
         <v>0.1295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3179314811658259</v>
+        <v>0.3093752977409235</v>
       </c>
       <c r="J9" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K9" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1002646543414303</v>
+        <v>0.09548417420847721</v>
       </c>
       <c r="M9" t="n">
-        <v>5.665777988282497</v>
+        <v>5.67753641312957</v>
       </c>
       <c r="N9" t="n">
-        <v>52.43881087517025</v>
+        <v>52.69288720187289</v>
       </c>
       <c r="O9" t="n">
-        <v>7.241464691287962</v>
+        <v>7.258986651170595</v>
       </c>
       <c r="P9" t="n">
-        <v>385.688707125489</v>
+        <v>385.7738536207017</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29889,28 +29999,28 @@
         <v>0.1507</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2360689589116613</v>
+        <v>0.227024433637137</v>
       </c>
       <c r="J10" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K10" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05920694872111121</v>
+        <v>0.05495713528799806</v>
       </c>
       <c r="M10" t="n">
-        <v>5.580754473101058</v>
+        <v>5.598651962965534</v>
       </c>
       <c r="N10" t="n">
-        <v>51.19387903384432</v>
+        <v>51.50727527836263</v>
       </c>
       <c r="O10" t="n">
-        <v>7.154989799702325</v>
+        <v>7.176856921965396</v>
       </c>
       <c r="P10" t="n">
-        <v>393.1297339024857</v>
+        <v>393.2197397955843</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29967,28 +30077,28 @@
         <v>0.1119</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2457826757148033</v>
+        <v>0.2388983656532053</v>
       </c>
       <c r="J11" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K11" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07386513048024312</v>
+        <v>0.07022616134501314</v>
       </c>
       <c r="M11" t="n">
-        <v>5.279866914775174</v>
+        <v>5.291302461263514</v>
       </c>
       <c r="N11" t="n">
-        <v>43.78810488409722</v>
+        <v>43.91376800466806</v>
       </c>
       <c r="O11" t="n">
-        <v>6.617258109224486</v>
+        <v>6.626746411676552</v>
       </c>
       <c r="P11" t="n">
-        <v>395.7126266186547</v>
+        <v>395.7811355440057</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30045,28 +30155,28 @@
         <v>0.1089</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2314882669214886</v>
+        <v>0.2236838823944406</v>
       </c>
       <c r="J12" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K12" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05921079352244507</v>
+        <v>0.05557711692034728</v>
       </c>
       <c r="M12" t="n">
-        <v>5.533102262168499</v>
+        <v>5.546131039012828</v>
       </c>
       <c r="N12" t="n">
-        <v>49.22302039693786</v>
+        <v>49.4123859749497</v>
       </c>
       <c r="O12" t="n">
-        <v>7.01591194335689</v>
+        <v>7.029394424482788</v>
       </c>
       <c r="P12" t="n">
-        <v>401.2864941590378</v>
+        <v>401.3641590953541</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30104,7 +30214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M506"/>
+  <dimension ref="A1:M508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64009,6 +64119,140 @@
         </is>
       </c>
     </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-09 22:11:38+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-34.82208730297235,173.40826860674565</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-34.8226612879223,173.40773990391037</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>-34.82330238428436,173.40739474099811</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>-34.82399137836083,173.40720550440568</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>-34.82468906482461,173.40704654508087</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>-34.825402114146506,173.40696120800308</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>-34.82612889160687,173.40698778145557</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>-34.82683486213568,173.40710349703372</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>-34.8274672182692,173.40742322283842</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>-34.827955513602966,173.40796825796698</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>-34.82831812142359,173.408688862321</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-34.82209354832371,173.40827781050837</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-34.822666340879714,173.40774922376653</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-34.823305972115186,173.40740572024745</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-34.823993210474086,173.4072155404778</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>-34.82468991474381,173.40705787093827</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>-34.825402025279345,173.40696973688821</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>-34.82612844425803,173.40699464938862</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>-34.82683361130173,173.4071102173527</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>-34.82746354339872,173.40743138012974</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>-34.827952234295665,173.40797201055224</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>-34.82831359698981,173.40869265624585</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0024/nzd0024.xlsx
+++ b/data/nzd0024/nzd0024.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M508"/>
+  <dimension ref="A1:M509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23310,6 +23310,51 @@
       <c r="M508" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>378.03</v>
+      </c>
+      <c r="C509" t="n">
+        <v>381.69</v>
+      </c>
+      <c r="D509" t="n">
+        <v>386.86</v>
+      </c>
+      <c r="E509" t="n">
+        <v>391.22</v>
+      </c>
+      <c r="F509" t="n">
+        <v>389.64</v>
+      </c>
+      <c r="G509" t="n">
+        <v>383.61</v>
+      </c>
+      <c r="H509" t="n">
+        <v>381.53</v>
+      </c>
+      <c r="I509" t="n">
+        <v>384.64</v>
+      </c>
+      <c r="J509" t="n">
+        <v>389.35</v>
+      </c>
+      <c r="K509" t="n">
+        <v>394.35</v>
+      </c>
+      <c r="L509" t="n">
+        <v>398.39</v>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B588"/>
+  <dimension ref="A1:B591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29207,6 +29252,36 @@
       </c>
       <c r="B588" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -29375,28 +29450,28 @@
         <v>0.0737</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06568745699729708</v>
+        <v>0.0669628194457053</v>
       </c>
       <c r="J2" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K2" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006634709091948299</v>
+        <v>0.006920565306376636</v>
       </c>
       <c r="M2" t="n">
-        <v>4.937156159854426</v>
+        <v>4.934000789296086</v>
       </c>
       <c r="N2" t="n">
-        <v>37.54464028199069</v>
+        <v>37.4914512005024</v>
       </c>
       <c r="O2" t="n">
-        <v>6.127368136646491</v>
+        <v>6.123026310616541</v>
       </c>
       <c r="P2" t="n">
-        <v>373.0287710188523</v>
+        <v>373.0160618278983</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29453,28 +29528,28 @@
         <v>0.0822</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09706138126948115</v>
+        <v>0.09741013260464637</v>
       </c>
       <c r="J3" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K3" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02026499417581307</v>
+        <v>0.02049817262655507</v>
       </c>
       <c r="M3" t="n">
-        <v>4.044248346965619</v>
+        <v>4.037794186673858</v>
       </c>
       <c r="N3" t="n">
-        <v>26.46982261019803</v>
+        <v>26.41926585434214</v>
       </c>
       <c r="O3" t="n">
-        <v>5.14488314835216</v>
+        <v>5.139967495455797</v>
       </c>
       <c r="P3" t="n">
-        <v>378.2173747942406</v>
+        <v>378.2138994313588</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29531,28 +29606,28 @@
         <v>0.0805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1017922680989252</v>
+        <v>0.1013119686735166</v>
       </c>
       <c r="J4" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K4" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01783135739484321</v>
+        <v>0.01774428302532272</v>
       </c>
       <c r="M4" t="n">
-        <v>4.642392198112853</v>
+        <v>4.635744852463805</v>
       </c>
       <c r="N4" t="n">
-        <v>33.16860419976206</v>
+        <v>33.1062499859737</v>
       </c>
       <c r="O4" t="n">
-        <v>5.759219061623031</v>
+        <v>5.753803088912037</v>
       </c>
       <c r="P4" t="n">
-        <v>385.3788104723772</v>
+        <v>385.383596733036</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29609,28 +29684,28 @@
         <v>0.0893</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1465190967622057</v>
+        <v>0.1459104214401447</v>
       </c>
       <c r="J5" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K5" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03259534224317762</v>
+        <v>0.03247292251989564</v>
       </c>
       <c r="M5" t="n">
-        <v>4.880304916549104</v>
+        <v>4.874033288998228</v>
       </c>
       <c r="N5" t="n">
-        <v>37.02857915284205</v>
+        <v>36.9604072001616</v>
       </c>
       <c r="O5" t="n">
-        <v>6.085111268731414</v>
+        <v>6.079507151090588</v>
       </c>
       <c r="P5" t="n">
-        <v>388.877822519189</v>
+        <v>388.883888066208</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29687,28 +29762,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2622846450919479</v>
+        <v>0.259649434323843</v>
       </c>
       <c r="J6" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K6" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09646225213936055</v>
+        <v>0.09490515208542272</v>
       </c>
       <c r="M6" t="n">
-        <v>5.091957388906228</v>
+        <v>5.095524825259736</v>
       </c>
       <c r="N6" t="n">
-        <v>37.44816920395539</v>
+        <v>37.46290375501452</v>
       </c>
       <c r="O6" t="n">
-        <v>6.119490926862739</v>
+        <v>6.120694711796571</v>
       </c>
       <c r="P6" t="n">
-        <v>389.3882074768092</v>
+        <v>389.4144677739488</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29765,28 +29840,28 @@
         <v>0.0825</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1641554631614079</v>
+        <v>0.1605186818975707</v>
       </c>
       <c r="J7" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K7" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03275970389434568</v>
+        <v>0.03139723512147674</v>
       </c>
       <c r="M7" t="n">
-        <v>5.624933982740917</v>
+        <v>5.628686688359106</v>
       </c>
       <c r="N7" t="n">
-        <v>46.23821381894994</v>
+        <v>46.31565823591194</v>
       </c>
       <c r="O7" t="n">
-        <v>6.799868661889723</v>
+        <v>6.805560831842732</v>
       </c>
       <c r="P7" t="n">
-        <v>388.5308917446702</v>
+        <v>388.5671328521277</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29843,28 +29918,28 @@
         <v>0.1961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2833426054283761</v>
+        <v>0.2802152630039886</v>
       </c>
       <c r="J8" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K8" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1084473254310864</v>
+        <v>0.1064447571535345</v>
       </c>
       <c r="M8" t="n">
-        <v>4.92897662822191</v>
+        <v>4.931564732575687</v>
       </c>
       <c r="N8" t="n">
-        <v>38.35728692614185</v>
+        <v>38.40635375522152</v>
       </c>
       <c r="O8" t="n">
-        <v>6.193325998697457</v>
+        <v>6.197285999146846</v>
       </c>
       <c r="P8" t="n">
-        <v>381.9784290274922</v>
+        <v>382.0095934953653</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29921,28 +29996,28 @@
         <v>0.1295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3093752977409235</v>
+        <v>0.3057097659949805</v>
       </c>
       <c r="J9" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K9" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09548417420847721</v>
+        <v>0.09355660077385475</v>
       </c>
       <c r="M9" t="n">
-        <v>5.67753641312957</v>
+        <v>5.680960972455336</v>
       </c>
       <c r="N9" t="n">
-        <v>52.69288720187289</v>
+        <v>52.76029968134856</v>
       </c>
       <c r="O9" t="n">
-        <v>7.258986651170595</v>
+        <v>7.263628547864253</v>
       </c>
       <c r="P9" t="n">
-        <v>385.7738536207017</v>
+        <v>385.8103812313156</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29999,28 +30074,28 @@
         <v>0.1507</v>
       </c>
       <c r="I10" t="n">
-        <v>0.227024433637137</v>
+        <v>0.2231427365709677</v>
       </c>
       <c r="J10" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K10" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05495713528799806</v>
+        <v>0.05323518779417113</v>
       </c>
       <c r="M10" t="n">
-        <v>5.598651962965534</v>
+        <v>5.604810620967973</v>
       </c>
       <c r="N10" t="n">
-        <v>51.50727527836263</v>
+        <v>51.59780173951593</v>
       </c>
       <c r="O10" t="n">
-        <v>7.176856921965396</v>
+        <v>7.18316098521507</v>
       </c>
       <c r="P10" t="n">
-        <v>393.2197397955843</v>
+        <v>393.2584215282173</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30077,28 +30152,28 @@
         <v>0.1119</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2388983656532053</v>
+        <v>0.2358487333212648</v>
       </c>
       <c r="J11" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K11" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07022616134501314</v>
+        <v>0.06868602482850072</v>
       </c>
       <c r="M11" t="n">
-        <v>5.291302461263514</v>
+        <v>5.295222887250758</v>
       </c>
       <c r="N11" t="n">
-        <v>43.91376800466806</v>
+        <v>43.94578285194929</v>
       </c>
       <c r="O11" t="n">
-        <v>6.626746411676552</v>
+        <v>6.629161549694598</v>
       </c>
       <c r="P11" t="n">
-        <v>395.7811355440057</v>
+        <v>395.8115256183681</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30155,28 +30230,28 @@
         <v>0.1089</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2236838823944406</v>
+        <v>0.2201898463781983</v>
       </c>
       <c r="J12" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K12" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05557711692034728</v>
+        <v>0.05401964664322145</v>
       </c>
       <c r="M12" t="n">
-        <v>5.546131039012828</v>
+        <v>5.550742011992897</v>
       </c>
       <c r="N12" t="n">
-        <v>49.4123859749497</v>
+        <v>49.47061694570488</v>
       </c>
       <c r="O12" t="n">
-        <v>7.029394424482788</v>
+        <v>7.033535167019846</v>
       </c>
       <c r="P12" t="n">
-        <v>401.3641590953541</v>
+        <v>401.3989777235691</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30214,7 +30289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M508"/>
+  <dimension ref="A1:M509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64253,6 +64328,73 @@
         </is>
       </c>
     </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-34.822099220706434,173.4082861698904</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-34.822671195681245,173.4077581781392</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-34.82330969282758,173.40741710613662</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-34.82399457481322,173.4072230141488</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>-34.824690813695675,173.4070698502108</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>-34.82540192843624,173.40697903118613</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>-34.82612813182369,173.40699944604026</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>-34.82683148686863,173.40712163122737</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>-34.82745913355346,173.40744116887836</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>-34.82794823354063,173.40797658870582</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>-34.82830936924011,173.40869620138838</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0024/nzd0024.xlsx
+++ b/data/nzd0024/nzd0024.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M509"/>
+  <dimension ref="A1:M512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23355,6 +23355,141 @@
       <c r="M509" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>378.4</v>
+      </c>
+      <c r="C510" t="n">
+        <v>382.94</v>
+      </c>
+      <c r="D510" t="n">
+        <v>388.74</v>
+      </c>
+      <c r="E510" t="n">
+        <v>394.02</v>
+      </c>
+      <c r="F510" t="n">
+        <v>391.22</v>
+      </c>
+      <c r="G510" t="n">
+        <v>385.59</v>
+      </c>
+      <c r="H510" t="n">
+        <v>381.75</v>
+      </c>
+      <c r="I510" t="n">
+        <v>386.25</v>
+      </c>
+      <c r="J510" t="n">
+        <v>389.88</v>
+      </c>
+      <c r="K510" t="n">
+        <v>394.75</v>
+      </c>
+      <c r="L510" t="n">
+        <v>398.59</v>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>378.4</v>
+      </c>
+      <c r="C511" t="n">
+        <v>382.94</v>
+      </c>
+      <c r="D511" t="n">
+        <v>388.74</v>
+      </c>
+      <c r="E511" t="n">
+        <v>394.02</v>
+      </c>
+      <c r="F511" t="n">
+        <v>391.22</v>
+      </c>
+      <c r="G511" t="n">
+        <v>385.59</v>
+      </c>
+      <c r="H511" t="n">
+        <v>381.75</v>
+      </c>
+      <c r="I511" t="n">
+        <v>385.9</v>
+      </c>
+      <c r="J511" t="n">
+        <v>389.77</v>
+      </c>
+      <c r="K511" t="n">
+        <v>394.75</v>
+      </c>
+      <c r="L511" t="n">
+        <v>398.25</v>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>376.62</v>
+      </c>
+      <c r="C512" t="n">
+        <v>381.45</v>
+      </c>
+      <c r="D512" t="n">
+        <v>388.13</v>
+      </c>
+      <c r="E512" t="n">
+        <v>393.24</v>
+      </c>
+      <c r="F512" t="n">
+        <v>391.65</v>
+      </c>
+      <c r="G512" t="n">
+        <v>386.49</v>
+      </c>
+      <c r="H512" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="I512" t="n">
+        <v>386.01</v>
+      </c>
+      <c r="J512" t="n">
+        <v>389.83</v>
+      </c>
+      <c r="K512" t="n">
+        <v>395.13</v>
+      </c>
+      <c r="L512" t="n">
+        <v>398.83</v>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23369,7 +23504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B591"/>
+  <dimension ref="A1:B595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29282,6 +29417,46 @@
       </c>
       <c r="B591" t="n">
         <v>0.95</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -29450,28 +29625,28 @@
         <v>0.0737</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0669628194457053</v>
+        <v>0.07046191473250075</v>
       </c>
       <c r="J2" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K2" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006920565306376636</v>
+        <v>0.007750970285064107</v>
       </c>
       <c r="M2" t="n">
-        <v>4.934000789296086</v>
+        <v>4.922860732304167</v>
       </c>
       <c r="N2" t="n">
-        <v>37.4914512005024</v>
+        <v>37.32727799357129</v>
       </c>
       <c r="O2" t="n">
-        <v>6.123026310616541</v>
+        <v>6.109605387712965</v>
       </c>
       <c r="P2" t="n">
-        <v>373.0160618278983</v>
+        <v>372.9809877545705</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29528,28 +29703,28 @@
         <v>0.0822</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09741013260464637</v>
+        <v>0.09930744092402211</v>
       </c>
       <c r="J3" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K3" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02049817262655507</v>
+        <v>0.02156188249160551</v>
       </c>
       <c r="M3" t="n">
-        <v>4.037794186673858</v>
+        <v>4.022316712891058</v>
       </c>
       <c r="N3" t="n">
-        <v>26.41926585434214</v>
+        <v>26.28228369579962</v>
       </c>
       <c r="O3" t="n">
-        <v>5.139967495455797</v>
+        <v>5.12662498099867</v>
       </c>
       <c r="P3" t="n">
-        <v>378.2138994313588</v>
+        <v>378.194882479568</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29606,28 +29781,28 @@
         <v>0.0805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1013119686735166</v>
+        <v>0.1018275407679884</v>
       </c>
       <c r="J4" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K4" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01774428302532272</v>
+        <v>0.01816550803563166</v>
       </c>
       <c r="M4" t="n">
-        <v>4.635744852463805</v>
+        <v>4.610995660443465</v>
       </c>
       <c r="N4" t="n">
-        <v>33.1062499859737</v>
+        <v>32.91350067273757</v>
       </c>
       <c r="O4" t="n">
-        <v>5.753803088912037</v>
+        <v>5.73702890638853</v>
       </c>
       <c r="P4" t="n">
-        <v>385.383596733036</v>
+        <v>385.3784295661059</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29684,28 +29859,28 @@
         <v>0.0893</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1459104214401447</v>
+        <v>0.1470523003009671</v>
       </c>
       <c r="J5" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K5" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03247292251989564</v>
+        <v>0.03340315368167213</v>
       </c>
       <c r="M5" t="n">
-        <v>4.874033288998228</v>
+        <v>4.850539705814905</v>
       </c>
       <c r="N5" t="n">
-        <v>36.9604072001616</v>
+        <v>36.74974891685611</v>
       </c>
       <c r="O5" t="n">
-        <v>6.079507151090588</v>
+        <v>6.062157117467025</v>
       </c>
       <c r="P5" t="n">
-        <v>388.883888066208</v>
+        <v>388.8724426322367</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29762,28 +29937,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.259649434323843</v>
+        <v>0.2538269967113171</v>
       </c>
       <c r="J6" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K6" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09490515208542272</v>
+        <v>0.09190583951644338</v>
       </c>
       <c r="M6" t="n">
-        <v>5.095524825259736</v>
+        <v>5.095333525719972</v>
       </c>
       <c r="N6" t="n">
-        <v>37.46290375501452</v>
+        <v>37.38662208494124</v>
       </c>
       <c r="O6" t="n">
-        <v>6.120694711796571</v>
+        <v>6.11446008122886</v>
       </c>
       <c r="P6" t="n">
-        <v>389.4144677739488</v>
+        <v>389.4728362744432</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29840,28 +30015,28 @@
         <v>0.0825</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1605186818975707</v>
+        <v>0.1523899213606613</v>
       </c>
       <c r="J7" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K7" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03139723512147674</v>
+        <v>0.02859923814269938</v>
       </c>
       <c r="M7" t="n">
-        <v>5.628686688359106</v>
+        <v>5.628583542411876</v>
       </c>
       <c r="N7" t="n">
-        <v>46.31565823591194</v>
+        <v>46.32434578182526</v>
       </c>
       <c r="O7" t="n">
-        <v>6.805560831842732</v>
+        <v>6.806199070099644</v>
       </c>
       <c r="P7" t="n">
-        <v>388.5671328521277</v>
+        <v>388.6486209764825</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29918,28 +30093,28 @@
         <v>0.1961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2802152630039886</v>
+        <v>0.2711195755835349</v>
       </c>
       <c r="J8" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K8" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1064447571535345</v>
+        <v>0.1007501920479714</v>
       </c>
       <c r="M8" t="n">
-        <v>4.931564732575687</v>
+        <v>4.938082561421687</v>
       </c>
       <c r="N8" t="n">
-        <v>38.40635375522152</v>
+        <v>38.53089102494079</v>
       </c>
       <c r="O8" t="n">
-        <v>6.197285999146846</v>
+        <v>6.207325593598324</v>
       </c>
       <c r="P8" t="n">
-        <v>382.0095934953653</v>
+        <v>382.1007773844957</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29996,28 +30171,28 @@
         <v>0.1295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3057097659949805</v>
+        <v>0.296463233580004</v>
       </c>
       <c r="J9" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K9" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09355660077385475</v>
+        <v>0.08903496536954691</v>
       </c>
       <c r="M9" t="n">
-        <v>5.680960972455336</v>
+        <v>5.684005324631582</v>
       </c>
       <c r="N9" t="n">
-        <v>52.76029968134856</v>
+        <v>52.81236611844979</v>
       </c>
       <c r="O9" t="n">
-        <v>7.263628547864253</v>
+        <v>7.267211715537796</v>
       </c>
       <c r="P9" t="n">
-        <v>385.8103812313156</v>
+        <v>385.9030772098617</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30074,28 +30249,28 @@
         <v>0.1507</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2231427365709677</v>
+        <v>0.2121835460507531</v>
       </c>
       <c r="J10" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K10" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05323518779417113</v>
+        <v>0.04856257660788577</v>
       </c>
       <c r="M10" t="n">
-        <v>5.604810620967973</v>
+        <v>5.619786773912218</v>
       </c>
       <c r="N10" t="n">
-        <v>51.59780173951593</v>
+        <v>51.80298004683004</v>
       </c>
       <c r="O10" t="n">
-        <v>7.18316098521507</v>
+        <v>7.197428710784848</v>
       </c>
       <c r="P10" t="n">
-        <v>393.2584215282173</v>
+        <v>393.3682865618184</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30152,28 +30327,28 @@
         <v>0.1119</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2358487333212648</v>
+        <v>0.2274062020409396</v>
       </c>
       <c r="J11" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K11" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06868602482850072</v>
+        <v>0.06458236081691004</v>
       </c>
       <c r="M11" t="n">
-        <v>5.295222887250758</v>
+        <v>5.303466501419806</v>
       </c>
       <c r="N11" t="n">
-        <v>43.94578285194929</v>
+        <v>43.98950526433823</v>
       </c>
       <c r="O11" t="n">
-        <v>6.629161549694598</v>
+        <v>6.632458463069198</v>
       </c>
       <c r="P11" t="n">
-        <v>395.8115256183681</v>
+        <v>395.8961604661585</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30230,28 +30405,28 @@
         <v>0.1089</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2201898463781983</v>
+        <v>0.2100082976804439</v>
       </c>
       <c r="J12" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K12" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05401964664322145</v>
+        <v>0.04961106065221055</v>
       </c>
       <c r="M12" t="n">
-        <v>5.550742011992897</v>
+        <v>5.562563222144265</v>
       </c>
       <c r="N12" t="n">
-        <v>49.47061694570488</v>
+        <v>49.61906764857905</v>
       </c>
       <c r="O12" t="n">
-        <v>7.033535167019846</v>
+        <v>7.04408032666998</v>
       </c>
       <c r="P12" t="n">
-        <v>401.3989777235691</v>
+        <v>401.5010460831344</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30289,7 +30464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M509"/>
+  <dimension ref="A1:M512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64395,6 +64570,207 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-34.8221013406877,173.40828929410418</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-34.82267738802914,173.40776959953442</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-34.82331593830669,173.4074362181672</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-34.824000032165124,173.40725290883523</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-34.824692104915364,173.40708705680268</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-34.82540170284601,173.40700068143286</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-34.82612797560643,173.40700184436605</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>-34.8268282902897,173.4071388053741</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>-34.82745684216296,173.4074462551885</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>-34.8279456100946,173.40797959077352</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>-34.82830788581913,173.40869744529797</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-34.8221013406877,173.40828929410418</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-34.82267738802914,173.40776959953442</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-34.82331593830669,173.4074362181672</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-34.824000032165124,173.40725290883523</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-34.824692104915364,173.40708705680268</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-34.82540170284601,173.40700068143286</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-34.82612797560643,173.40700184436605</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-34.826828985198354,173.40713507186408</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>-34.82745731773459,173.40744519953924</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>-34.8279456100946,173.40797959077352</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>-34.82831040763479,173.40869533065168</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-34.82209114185813,173.4082742641042</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-34.82267000675031,173.4077559852315</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-34.82331391184839,173.40743001692292</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-34.82399851190355,173.40724458102932</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-34.82469245632284,173.40709173960943</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-34.825401600303735,173.40701052245407</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-34.8261280821182,173.40700020914394</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-34.826828766798506,173.40713624525296</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>-34.82745705833188,173.40744577534792</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>-34.827943117820816,173.40798244273765</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>-34.828306105713956,173.4086989379894</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0024/nzd0024.xlsx
+++ b/data/nzd0024/nzd0024.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M512"/>
+  <dimension ref="A1:M516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23490,6 +23490,186 @@
       <c r="M512" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:57+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>375.87</v>
+      </c>
+      <c r="C513" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="D513" t="n">
+        <v>387.27</v>
+      </c>
+      <c r="E513" t="n">
+        <v>393.26</v>
+      </c>
+      <c r="F513" t="n">
+        <v>392.38</v>
+      </c>
+      <c r="G513" t="n">
+        <v>387.27</v>
+      </c>
+      <c r="H513" t="n">
+        <v>381.99</v>
+      </c>
+      <c r="I513" t="n">
+        <v>385.83</v>
+      </c>
+      <c r="J513" t="n">
+        <v>390.04</v>
+      </c>
+      <c r="K513" t="n">
+        <v>395.05</v>
+      </c>
+      <c r="L513" t="n">
+        <v>398.67</v>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>374.16</v>
+      </c>
+      <c r="C514" t="n">
+        <v>380.59</v>
+      </c>
+      <c r="D514" t="n">
+        <v>386.16</v>
+      </c>
+      <c r="E514" t="n">
+        <v>392.71</v>
+      </c>
+      <c r="F514" t="n">
+        <v>391.71</v>
+      </c>
+      <c r="G514" t="n">
+        <v>386.82</v>
+      </c>
+      <c r="H514" t="n">
+        <v>381.82</v>
+      </c>
+      <c r="I514" t="n">
+        <v>385.27</v>
+      </c>
+      <c r="J514" t="n">
+        <v>389.99</v>
+      </c>
+      <c r="K514" t="n">
+        <v>394.77</v>
+      </c>
+      <c r="L514" t="n">
+        <v>398.06</v>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>374.16</v>
+      </c>
+      <c r="C515" t="n">
+        <v>379.32</v>
+      </c>
+      <c r="D515" t="n">
+        <v>385.08</v>
+      </c>
+      <c r="E515" t="n">
+        <v>391.77</v>
+      </c>
+      <c r="F515" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="G515" t="n">
+        <v>385.88</v>
+      </c>
+      <c r="H515" t="n">
+        <v>381.44</v>
+      </c>
+      <c r="I515" t="n">
+        <v>384.75</v>
+      </c>
+      <c r="J515" t="n">
+        <v>389.74</v>
+      </c>
+      <c r="K515" t="n">
+        <v>394.37</v>
+      </c>
+      <c r="L515" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>372.12</v>
+      </c>
+      <c r="C516" t="n">
+        <v>377.87</v>
+      </c>
+      <c r="D516" t="n">
+        <v>384.89</v>
+      </c>
+      <c r="E516" t="n">
+        <v>391.47</v>
+      </c>
+      <c r="F516" t="n">
+        <v>392.05</v>
+      </c>
+      <c r="G516" t="n">
+        <v>386.42</v>
+      </c>
+      <c r="H516" t="n">
+        <v>381.32</v>
+      </c>
+      <c r="I516" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="J516" t="n">
+        <v>389.69</v>
+      </c>
+      <c r="K516" t="n">
+        <v>395.24</v>
+      </c>
+      <c r="L516" t="n">
+        <v>397.67</v>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23504,7 +23684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B595"/>
+  <dimension ref="A1:B599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29457,6 +29637,46 @@
       </c>
       <c r="B595" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -29625,28 +29845,28 @@
         <v>0.0737</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07046191473250075</v>
+        <v>0.06925779611668013</v>
       </c>
       <c r="J2" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K2" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007750970285064107</v>
+        <v>0.007621358206285178</v>
       </c>
       <c r="M2" t="n">
-        <v>4.922860732304167</v>
+        <v>4.894494313146248</v>
       </c>
       <c r="N2" t="n">
-        <v>37.32727799357129</v>
+        <v>37.05580549681425</v>
       </c>
       <c r="O2" t="n">
-        <v>6.109605387712965</v>
+        <v>6.087347985519988</v>
       </c>
       <c r="P2" t="n">
-        <v>372.9809877545705</v>
+        <v>372.9931009503293</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29703,28 +29923,28 @@
         <v>0.0822</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09930744092402211</v>
+        <v>0.09776893985694238</v>
       </c>
       <c r="J3" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K3" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02156188249160551</v>
+        <v>0.02126586176200651</v>
       </c>
       <c r="M3" t="n">
-        <v>4.022316712891058</v>
+        <v>4.002742062492797</v>
       </c>
       <c r="N3" t="n">
-        <v>26.28228369579962</v>
+        <v>26.1010182756956</v>
       </c>
       <c r="O3" t="n">
-        <v>5.12662498099867</v>
+        <v>5.108915567485491</v>
       </c>
       <c r="P3" t="n">
-        <v>378.194882479568</v>
+        <v>378.210354215258</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29781,28 +30001,28 @@
         <v>0.0805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1018275407679884</v>
+        <v>0.09839842045588312</v>
       </c>
       <c r="J4" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K4" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01816550803563166</v>
+        <v>0.01726218208507146</v>
       </c>
       <c r="M4" t="n">
-        <v>4.610995660443465</v>
+        <v>4.59321917353558</v>
       </c>
       <c r="N4" t="n">
-        <v>32.91350067273757</v>
+        <v>32.70334063645542</v>
       </c>
       <c r="O4" t="n">
-        <v>5.73702890638853</v>
+        <v>5.718683470559935</v>
       </c>
       <c r="P4" t="n">
-        <v>385.3784295661059</v>
+        <v>385.4128807264908</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29859,28 +30079,28 @@
         <v>0.0893</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1470523003009671</v>
+        <v>0.1462795509423012</v>
       </c>
       <c r="J5" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K5" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03340315368167213</v>
+        <v>0.03363888803548432</v>
       </c>
       <c r="M5" t="n">
-        <v>4.850539705814905</v>
+        <v>4.818924582089144</v>
       </c>
       <c r="N5" t="n">
-        <v>36.74974891685611</v>
+        <v>36.47026666377786</v>
       </c>
       <c r="O5" t="n">
-        <v>6.062157117467025</v>
+        <v>6.039061737039775</v>
       </c>
       <c r="P5" t="n">
-        <v>388.8724426322367</v>
+        <v>388.8802129202022</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29937,28 +30157,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2538269967113171</v>
+        <v>0.247195980230492</v>
       </c>
       <c r="J6" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K6" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09190583951644338</v>
+        <v>0.08871378906756311</v>
       </c>
       <c r="M6" t="n">
-        <v>5.095333525719972</v>
+        <v>5.08958912915205</v>
       </c>
       <c r="N6" t="n">
-        <v>37.38662208494124</v>
+        <v>37.24091704428812</v>
       </c>
       <c r="O6" t="n">
-        <v>6.11446008122886</v>
+        <v>6.102533657775933</v>
       </c>
       <c r="P6" t="n">
-        <v>389.4728362744432</v>
+        <v>389.5394333732302</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30015,28 +30235,28 @@
         <v>0.0825</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1523899213606613</v>
+        <v>0.1430619534452245</v>
       </c>
       <c r="J7" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K7" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02859923814269938</v>
+        <v>0.02558260387629419</v>
       </c>
       <c r="M7" t="n">
-        <v>5.628583542411876</v>
+        <v>5.622792551360169</v>
       </c>
       <c r="N7" t="n">
-        <v>46.32434578182526</v>
+        <v>46.25114329026308</v>
       </c>
       <c r="O7" t="n">
-        <v>6.806199070099644</v>
+        <v>6.800819310220136</v>
       </c>
       <c r="P7" t="n">
-        <v>388.6486209764825</v>
+        <v>388.7423070887763</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30093,28 +30313,28 @@
         <v>0.1961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2711195755835349</v>
+        <v>0.2593828660442533</v>
       </c>
       <c r="J8" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K8" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1007501920479714</v>
+        <v>0.09353822728371874</v>
       </c>
       <c r="M8" t="n">
-        <v>4.938082561421687</v>
+        <v>4.94648226320093</v>
       </c>
       <c r="N8" t="n">
-        <v>38.53089102494079</v>
+        <v>38.68270328429014</v>
       </c>
       <c r="O8" t="n">
-        <v>6.207325593598324</v>
+        <v>6.219542047795009</v>
       </c>
       <c r="P8" t="n">
-        <v>382.1007773844957</v>
+        <v>382.2186546348447</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30171,28 +30391,28 @@
         <v>0.1295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.296463233580004</v>
+        <v>0.2833757556718797</v>
       </c>
       <c r="J9" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K9" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08903496536954691</v>
+        <v>0.08253042299925473</v>
       </c>
       <c r="M9" t="n">
-        <v>5.684005324631582</v>
+        <v>5.691742076336944</v>
       </c>
       <c r="N9" t="n">
-        <v>52.81236611844979</v>
+        <v>52.96352378236224</v>
       </c>
       <c r="O9" t="n">
-        <v>7.267211715537796</v>
+        <v>7.277604261181164</v>
       </c>
       <c r="P9" t="n">
-        <v>385.9030772098617</v>
+        <v>386.034520006237</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30249,28 +30469,28 @@
         <v>0.1507</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2121835460507531</v>
+        <v>0.1982112629597285</v>
       </c>
       <c r="J10" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K10" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04856257660788577</v>
+        <v>0.04287155325498315</v>
       </c>
       <c r="M10" t="n">
-        <v>5.619786773912218</v>
+        <v>5.636698052216658</v>
       </c>
       <c r="N10" t="n">
-        <v>51.80298004683004</v>
+        <v>52.03931263555621</v>
       </c>
       <c r="O10" t="n">
-        <v>7.197428710784848</v>
+        <v>7.213827876762531</v>
       </c>
       <c r="P10" t="n">
-        <v>393.3682865618184</v>
+        <v>393.5086143801822</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30327,28 +30547,28 @@
         <v>0.1119</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2274062020409396</v>
+        <v>0.2165688319524523</v>
       </c>
       <c r="J11" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K11" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06458236081691004</v>
+        <v>0.0594396062210244</v>
       </c>
       <c r="M11" t="n">
-        <v>5.303466501419806</v>
+        <v>5.312394119856193</v>
       </c>
       <c r="N11" t="n">
-        <v>43.98950526433823</v>
+        <v>44.03282611089542</v>
       </c>
       <c r="O11" t="n">
-        <v>6.632458463069198</v>
+        <v>6.635723480593161</v>
       </c>
       <c r="P11" t="n">
-        <v>395.8961604661585</v>
+        <v>396.005000008458</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30405,28 +30625,28 @@
         <v>0.1089</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2100082976804439</v>
+        <v>0.1960919434382852</v>
       </c>
       <c r="J12" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K12" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04961106065221055</v>
+        <v>0.04374610761178421</v>
       </c>
       <c r="M12" t="n">
-        <v>5.562563222144265</v>
+        <v>5.579621623131302</v>
       </c>
       <c r="N12" t="n">
-        <v>49.61906764857905</v>
+        <v>49.86860147365138</v>
       </c>
       <c r="O12" t="n">
-        <v>7.04408032666998</v>
+        <v>7.061770420627633</v>
       </c>
       <c r="P12" t="n">
-        <v>401.5010460831344</v>
+        <v>401.6408149331186</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30464,7 +30684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M512"/>
+  <dimension ref="A1:M516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64771,6 +64991,274 @@
         </is>
       </c>
     </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:57+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-34.82208684459792,173.40826793124018</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-34.82267074983214,173.4077573557988</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-34.82331105487381,173.4074212741856</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-34.82399855088462,173.4072447945628</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-34.8246930528979,173.40709968949074</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-34.8254015114331,173.4070190513391</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-34.82612780518758,173.40700446072148</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-34.82682912418008,173.40713432516205</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-34.82745615042239,173.4074477906783</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>-34.827943642510036,173.40798184232418</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-34.82830729245074,173.40869794286178</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-34.82207704684334,173.40825349231258</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-34.82266574641417,173.4077481273128</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-34.82330736738245,173.40740998995577</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-34.82399747890497,173.40723892239214</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-34.82469250535642,173.40709239302433</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-34.82540156270469,173.40701413082851</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-34.82612792590094,173.4070026074697</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-34.82683023603368,173.40712835154582</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-34.82745636659131,173.40744731083774</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>-34.8279454789223,173.4079797408769</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>-34.82831181688469,173.40869414893749</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-34.82207704684334,173.40825349231258</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-34.82265945498659,173.40773652317853</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-34.82330377955201,173.4073990107061</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-34.82399564679364,173.40722888631905</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-34.82469233373886,173.4070901060722</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-34.8254016698047,173.40700385242857</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-34.826128195730725,173.406998464907</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-34.82683126846891,173.40712280461634</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-34.82745744743595,173.4074449116349</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>-34.82794810236834,173.40797673880923</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>-34.82831597046328,173.40869066599026</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-34.82206535829176,173.40823626692975</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-34.82265227185926,173.40772327436596</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-34.82330314835953,173.4073970791715</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-34.823995062077095,173.40722568331708</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-34.824692783213344,173.40709609570874</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-34.82540160827927,173.4070097570413</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-34.826128280940104,173.40699715672926</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-34.8268305735606,173.4071265381266</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>-34.82745766360486,173.40744443179432</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>-34.82794239637313,173.4079832683062</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>-34.82831470955551,173.40869172331358</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0024/nzd0024.xlsx
+++ b/data/nzd0024/nzd0024.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M516"/>
+  <dimension ref="A1:M520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23670,6 +23670,186 @@
       <c r="M516" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>369.53</v>
+      </c>
+      <c r="C517" t="n">
+        <v>378.87</v>
+      </c>
+      <c r="D517" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="E517" t="n">
+        <v>391.89</v>
+      </c>
+      <c r="F517" t="n">
+        <v>392.3</v>
+      </c>
+      <c r="G517" t="n">
+        <v>386.22</v>
+      </c>
+      <c r="H517" t="n">
+        <v>382.62</v>
+      </c>
+      <c r="I517" t="n">
+        <v>385.57</v>
+      </c>
+      <c r="J517" t="n">
+        <v>389.31</v>
+      </c>
+      <c r="K517" t="n">
+        <v>395.17</v>
+      </c>
+      <c r="L517" t="n">
+        <v>397.17</v>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>368.84</v>
+      </c>
+      <c r="C518" t="n">
+        <v>378.76</v>
+      </c>
+      <c r="D518" t="n">
+        <v>385.26</v>
+      </c>
+      <c r="E518" t="n">
+        <v>391.06</v>
+      </c>
+      <c r="F518" t="n">
+        <v>392.31</v>
+      </c>
+      <c r="G518" t="n">
+        <v>386.31</v>
+      </c>
+      <c r="H518" t="n">
+        <v>382.83</v>
+      </c>
+      <c r="I518" t="n">
+        <v>385.95</v>
+      </c>
+      <c r="J518" t="n">
+        <v>389.79</v>
+      </c>
+      <c r="K518" t="n">
+        <v>395.55</v>
+      </c>
+      <c r="L518" t="n">
+        <v>397.99</v>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>365.96</v>
+      </c>
+      <c r="C519" t="n">
+        <v>376.52</v>
+      </c>
+      <c r="D519" t="n">
+        <v>386.51</v>
+      </c>
+      <c r="E519" t="n">
+        <v>389.58</v>
+      </c>
+      <c r="F519" t="n">
+        <v>391.29</v>
+      </c>
+      <c r="G519" t="n">
+        <v>387.33</v>
+      </c>
+      <c r="H519" t="n">
+        <v>384.08</v>
+      </c>
+      <c r="I519" t="n">
+        <v>386.15</v>
+      </c>
+      <c r="J519" t="n">
+        <v>390.2</v>
+      </c>
+      <c r="K519" t="n">
+        <v>396.09</v>
+      </c>
+      <c r="L519" t="n">
+        <v>397.74</v>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>365.44</v>
+      </c>
+      <c r="C520" t="n">
+        <v>375.68</v>
+      </c>
+      <c r="D520" t="n">
+        <v>386.38</v>
+      </c>
+      <c r="E520" t="n">
+        <v>389.86</v>
+      </c>
+      <c r="F520" t="n">
+        <v>391.32</v>
+      </c>
+      <c r="G520" t="n">
+        <v>387.62</v>
+      </c>
+      <c r="H520" t="n">
+        <v>383.69</v>
+      </c>
+      <c r="I520" t="n">
+        <v>386.31</v>
+      </c>
+      <c r="J520" t="n">
+        <v>390.59</v>
+      </c>
+      <c r="K520" t="n">
+        <v>396.5</v>
+      </c>
+      <c r="L520" t="n">
+        <v>398.21</v>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23684,7 +23864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B599"/>
+  <dimension ref="A1:B603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29677,6 +29857,46 @@
       </c>
       <c r="B599" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -29845,28 +30065,28 @@
         <v>0.0737</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06925779611668013</v>
+        <v>0.05815322646787028</v>
       </c>
       <c r="J2" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K2" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007621358206285178</v>
+        <v>0.005417220447415216</v>
       </c>
       <c r="M2" t="n">
-        <v>4.894494313146248</v>
+        <v>4.911867141637939</v>
       </c>
       <c r="N2" t="n">
-        <v>37.05580549681425</v>
+        <v>37.20719971409083</v>
       </c>
       <c r="O2" t="n">
-        <v>6.087347985519988</v>
+        <v>6.099770464049514</v>
       </c>
       <c r="P2" t="n">
-        <v>372.9931009503293</v>
+        <v>373.1051943057508</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29923,28 +30143,28 @@
         <v>0.0822</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09776893985694238</v>
+        <v>0.09269911458486363</v>
       </c>
       <c r="J3" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K3" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02126586176200651</v>
+        <v>0.01942057558889532</v>
       </c>
       <c r="M3" t="n">
-        <v>4.002742062492797</v>
+        <v>4.001156789406768</v>
       </c>
       <c r="N3" t="n">
-        <v>26.1010182756956</v>
+        <v>26.00080409341336</v>
       </c>
       <c r="O3" t="n">
-        <v>5.108915567485491</v>
+        <v>5.099098360829428</v>
       </c>
       <c r="P3" t="n">
-        <v>378.210354215258</v>
+        <v>378.2615349489321</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30001,28 +30221,28 @@
         <v>0.0805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09839842045588312</v>
+        <v>0.09507686284673172</v>
       </c>
       <c r="J4" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K4" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01726218208507146</v>
+        <v>0.01639906831262605</v>
       </c>
       <c r="M4" t="n">
-        <v>4.59321917353558</v>
+        <v>4.575095224898786</v>
       </c>
       <c r="N4" t="n">
-        <v>32.70334063645542</v>
+        <v>32.49109675186318</v>
       </c>
       <c r="O4" t="n">
-        <v>5.718683470559935</v>
+        <v>5.700096205491902</v>
       </c>
       <c r="P4" t="n">
-        <v>385.4128807264908</v>
+        <v>385.4464014509854</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30079,28 +30299,28 @@
         <v>0.0893</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1462795509423012</v>
+        <v>0.142960934615131</v>
       </c>
       <c r="J5" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K5" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03363888803548432</v>
+        <v>0.03269723231967514</v>
       </c>
       <c r="M5" t="n">
-        <v>4.818924582089144</v>
+        <v>4.800024666399662</v>
       </c>
       <c r="N5" t="n">
-        <v>36.47026666377786</v>
+        <v>36.23273545453888</v>
       </c>
       <c r="O5" t="n">
-        <v>6.039061737039775</v>
+        <v>6.019363376183471</v>
       </c>
       <c r="P5" t="n">
-        <v>388.8802129202022</v>
+        <v>388.9137148099099</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30157,28 +30377,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.247195980230492</v>
+        <v>0.2406358575195141</v>
       </c>
       <c r="J6" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K6" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08871378906756311</v>
+        <v>0.08553236850991019</v>
       </c>
       <c r="M6" t="n">
-        <v>5.08958912915205</v>
+        <v>5.083873000828252</v>
       </c>
       <c r="N6" t="n">
-        <v>37.24091704428812</v>
+        <v>37.09996100253642</v>
       </c>
       <c r="O6" t="n">
-        <v>6.102533657775933</v>
+        <v>6.090973731886916</v>
       </c>
       <c r="P6" t="n">
-        <v>389.5394333732302</v>
+        <v>389.6056495190303</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30235,28 +30455,28 @@
         <v>0.0825</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1430619534452245</v>
+        <v>0.134500852479588</v>
       </c>
       <c r="J7" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K7" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02558260387629419</v>
+        <v>0.02295475570833816</v>
       </c>
       <c r="M7" t="n">
-        <v>5.622792551360169</v>
+        <v>5.613706462159834</v>
       </c>
       <c r="N7" t="n">
-        <v>46.25114329026308</v>
+        <v>46.14312486945801</v>
       </c>
       <c r="O7" t="n">
-        <v>6.800819310220136</v>
+        <v>6.792873093872577</v>
       </c>
       <c r="P7" t="n">
-        <v>388.7423070887763</v>
+        <v>388.8287113805496</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30313,28 +30533,28 @@
         <v>0.1961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2593828660442533</v>
+        <v>0.2505671424741843</v>
       </c>
       <c r="J8" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K8" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09353822728371874</v>
+        <v>0.08871431830209831</v>
       </c>
       <c r="M8" t="n">
-        <v>4.94648226320093</v>
+        <v>4.943492345236061</v>
       </c>
       <c r="N8" t="n">
-        <v>38.68270328429014</v>
+        <v>38.64773046449727</v>
       </c>
       <c r="O8" t="n">
-        <v>6.219542047795009</v>
+        <v>6.216729885116232</v>
       </c>
       <c r="P8" t="n">
-        <v>382.2186546348447</v>
+        <v>382.3076291676984</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30391,28 +30611,28 @@
         <v>0.1295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2833757556718797</v>
+        <v>0.271911182007769</v>
       </c>
       <c r="J9" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K9" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08253042299925473</v>
+        <v>0.07715321658218488</v>
       </c>
       <c r="M9" t="n">
-        <v>5.691742076336944</v>
+        <v>5.693138172690976</v>
       </c>
       <c r="N9" t="n">
-        <v>52.96352378236224</v>
+        <v>52.99618772442462</v>
       </c>
       <c r="O9" t="n">
-        <v>7.277604261181164</v>
+        <v>7.279848056410561</v>
       </c>
       <c r="P9" t="n">
-        <v>386.034520006237</v>
+        <v>386.1502322244261</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30469,28 +30689,28 @@
         <v>0.1507</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1982112629597285</v>
+        <v>0.1849347053028592</v>
       </c>
       <c r="J10" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K10" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04287155325498315</v>
+        <v>0.03775828130877101</v>
       </c>
       <c r="M10" t="n">
-        <v>5.636698052216658</v>
+        <v>5.650230047383388</v>
       </c>
       <c r="N10" t="n">
-        <v>52.03931263555621</v>
+        <v>52.23044570109328</v>
       </c>
       <c r="O10" t="n">
-        <v>7.213827876762531</v>
+        <v>7.22706342168749</v>
       </c>
       <c r="P10" t="n">
-        <v>393.5086143801822</v>
+        <v>393.6426138532746</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30547,28 +30767,28 @@
         <v>0.1119</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2165688319524523</v>
+        <v>0.2075829332531864</v>
       </c>
       <c r="J11" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K11" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0594396062210244</v>
+        <v>0.05547476500122517</v>
       </c>
       <c r="M11" t="n">
-        <v>5.312394119856193</v>
+        <v>5.312254762250831</v>
       </c>
       <c r="N11" t="n">
-        <v>44.03282611089542</v>
+        <v>43.96593480363041</v>
       </c>
       <c r="O11" t="n">
-        <v>6.635723480593161</v>
+        <v>6.630681322732259</v>
       </c>
       <c r="P11" t="n">
-        <v>396.005000008458</v>
+        <v>396.0956927653033</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30625,28 +30845,28 @@
         <v>0.1089</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1960919434382852</v>
+        <v>0.1824116002123759</v>
       </c>
       <c r="J12" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="K12" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04374610761178421</v>
+        <v>0.03826746587331553</v>
       </c>
       <c r="M12" t="n">
-        <v>5.579621623131302</v>
+        <v>5.5953257569572</v>
       </c>
       <c r="N12" t="n">
-        <v>49.86860147365138</v>
+        <v>50.11231189633239</v>
       </c>
       <c r="O12" t="n">
-        <v>7.061770420627633</v>
+        <v>7.079005007508639</v>
       </c>
       <c r="P12" t="n">
-        <v>401.6408149331186</v>
+        <v>401.7788914157231</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30684,7 +30904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M516"/>
+  <dimension ref="A1:M520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65259,6 +65479,274 @@
         </is>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-34.82205051841138,173.40821439745565</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-34.82265722574033,173.40773241147784</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-34.823304178199905,173.40740023062267</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-34.82399588068024,173.40723016751983</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-34.82469298751984,173.40709881827084</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-34.8254016310665,173.4070075701477</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-34.82612735783779,173.40701132865433</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-34.826829640397854,173.4071315516974</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>-34.827459306488585,173.4074407850059</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>-34.827942855476195,173.40798274294437</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>-34.82831841810776,173.40868861353903</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-34.82204656492906,173.40820857122642</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-34.82265668081345,173.40773140639547</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-34.82330437752383,173.40740084058095</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-34.82399426296432,173.40722130588114</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-34.82469299569209,173.4070989271733</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-34.82540162081225,173.4070085542498</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>-34.8261272087211,173.40701361796528</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>-34.82682888592571,173.40713560522263</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>-34.82745723126702,173.40744539147548</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>-34.82794036320234,173.40798559490833</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>-34.82831233608201,173.4086937135691</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-34.82203006343454,173.40818425305818</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-34.82264558411869,173.40771093926665</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-34.82330853010508,173.40741354804615</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-34.82399137836083,173.40720550440568</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>-34.82469216212125,173.40708781912005</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>-34.82540150459689,173.40701970740716</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-34.82612632112093,173.40702724481596</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>-34.82682848883505,173.40713773865696</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>-34.82745545868179,173.40744932616806</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>-34.82793682154987,173.4079896476989</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>-34.828314190358185,173.40869215868196</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-34.82202708399751,173.40817986227887</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-34.822641422857245,173.40770326409475</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-34.82330809823669,173.40741222646972</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-34.82399192409679,173.40720849387392</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-34.82469218663805,173.40708814582752</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>-34.825401471555075,173.40702287840284</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>-34.82612659805234,173.4070229932386</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>-34.82682817116249,173.40713944540437</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>-34.82745377256403,173.40745306892427</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>-34.82793413251738,173.40799272481743</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>-34.82831070431897,173.40869508186975</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
